--- a/forms/trg/Formulir_TRG_coastallaw.xlsx
+++ b/forms/trg/Formulir_TRG_coastallaw.xlsx
@@ -807,7 +807,7 @@
         </is>
       </c>
       <c r="B27" s="7">
-        <f>COUNTA(Anggota!B5:B23)</f>
+        <f>COUNTA(Anggota!B5:B24)</f>
         <v/>
       </c>
     </row>
@@ -818,7 +818,7 @@
         </is>
       </c>
       <c r="B28" s="7">
-        <f>COUNTA(Anggota!F5:F23)</f>
+        <f>COUNTA(Anggota!F5:F24)</f>
         <v/>
       </c>
     </row>
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M23"/>
+  <dimension ref="A1:M24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -949,12 +949,12 @@
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
-          <t>Dr. Kahar Lahae,S.H.,M.Hum</t>
+          <t>Prof. Dr. Farida Patittingi, S.H., M.Hum</t>
         </is>
       </c>
       <c r="C5" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Leader</t>
         </is>
       </c>
       <c r="D5" s="12" t="n"/>
@@ -978,12 +978,12 @@
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>Dr. Muh. Ilham Arisaputra, S.H., M.Kn.</t>
+          <t>Dr. Kahar Lahae,S.H.,M.Hum</t>
         </is>
       </c>
       <c r="C6" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D6" s="12" t="n"/>
@@ -1007,12 +1007,12 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>Dr. Aulia Rifai, S.H., M.H.</t>
+          <t>Dr. Muh. Ilham Arisaputra, S.H., M.Kn.</t>
         </is>
       </c>
       <c r="C7" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D7" s="12" t="n"/>
@@ -1036,12 +1036,12 @@
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>Santy Kouwagam, S.H., Ph.d</t>
+          <t>Dr. Aulia Rifai, S.H., M.H.</t>
         </is>
       </c>
       <c r="C8" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D8" s="12" t="n"/>
@@ -1065,12 +1065,12 @@
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>Andi Suci Wahyuni, S.H., M.Kn.</t>
+          <t>Santy Kouwagam, S.H., Ph.d</t>
         </is>
       </c>
       <c r="C9" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D9" s="12" t="n"/>
@@ -1094,12 +1094,12 @@
       </c>
       <c r="B10" s="11" t="inlineStr">
         <is>
-          <t>Amaliyah, S.H., M.H.</t>
+          <t>Andi Suci Wahyuni, S.H., M.Kn.</t>
         </is>
       </c>
       <c r="C10" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D10" s="12" t="n"/>
@@ -1123,12 +1123,12 @@
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t>Dr. Nuragifah,S.H.,M.H</t>
+          <t>Amaliyah, S.H., M.H.</t>
         </is>
       </c>
       <c r="C11" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D11" s="12" t="n"/>
@@ -1150,8 +1150,16 @@
       <c r="A12" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="B12" s="12" t="n"/>
-      <c r="C12" s="12" t="n"/>
+      <c r="B12" s="11" t="inlineStr">
+        <is>
+          <t>Dr. Nuragifah,S.H.,M.H</t>
+        </is>
+      </c>
+      <c r="C12" s="11" t="inlineStr">
+        <is>
+          <t>Researcher</t>
+        </is>
+      </c>
       <c r="D12" s="12" t="n"/>
       <c r="E12" s="11" t="n"/>
       <c r="F12" s="12" t="n"/>
@@ -1161,7 +1169,11 @@
       <c r="J12" s="12" t="n"/>
       <c r="K12" s="12" t="n"/>
       <c r="L12" s="12" t="n"/>
-      <c r="M12" s="12" t="n"/>
+      <c r="M12" s="11" t="inlineStr">
+        <is>
+          <t>Aktif</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="n">
@@ -1350,15 +1362,32 @@
       <c r="L23" s="12" t="n"/>
       <c r="M23" s="12" t="n"/>
     </row>
+    <row r="24">
+      <c r="A24" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="B24" s="12" t="n"/>
+      <c r="C24" s="12" t="n"/>
+      <c r="D24" s="12" t="n"/>
+      <c r="E24" s="11" t="n"/>
+      <c r="F24" s="12" t="n"/>
+      <c r="G24" s="12" t="n"/>
+      <c r="H24" s="12" t="n"/>
+      <c r="I24" s="12" t="n"/>
+      <c r="J24" s="12" t="n"/>
+      <c r="K24" s="12" t="n"/>
+      <c r="L24" s="12" t="n"/>
+      <c r="M24" s="12" t="n"/>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A2:M2"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation sqref="F5:H23" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F5:H24" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Daftar!$A$2:$A$39</formula1>
     </dataValidation>
-    <dataValidation sqref="M5:M23" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="M5:M24" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Daftar!$C$2:$C$3</formula1>
     </dataValidation>
   </dataValidations>
